--- a/AutosurveillanceTemplates/PLUVIO.xlsx
+++ b/AutosurveillanceTemplates/PLUVIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223EA670-D9AC-42DC-9A11-DA85327FB42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9508395E-3F15-4379-AC02-DD433B5A979C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pluvio" sheetId="48" r:id="rId1"/>
@@ -30,12 +30,13 @@
     <definedName name="LISTE_1">PARAM!$A$21:$A$23</definedName>
     <definedName name="LISTE_2">PARAM!$B$21:$B$24</definedName>
     <definedName name="LISTE_3">PARAM!$C$21:$C$25</definedName>
-    <definedName name="LISTE_4">PARAM!$D$21:$D$27</definedName>
+    <definedName name="LISTE_4">PARAM!$D$21:$D$25</definedName>
     <definedName name="LISTE_5">PARAM!$F$21:$F$25</definedName>
     <definedName name="LISTE_6">PARAM!$G$21</definedName>
+    <definedName name="LISTE_7">PARAM!$H$21:$H$23</definedName>
     <definedName name="Montage_sonde">PARAM!$G$44:$G$46</definedName>
-    <definedName name="Q_en_charge">PARAM!$A$30:$A$36</definedName>
-    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$39</definedName>
+    <definedName name="Q_en_charge">PARAM!$A$4:$A$30</definedName>
+    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$38</definedName>
     <definedName name="Satisfaction">PARAM!$D$44:$D$46</definedName>
     <definedName name="Type_capteur">PARAM!$C$44:$C$48</definedName>
     <definedName name="Type_equipement">PARAM!$C$4:$C$6</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="308">
   <si>
     <t>Pluviomètre</t>
   </si>
@@ -1744,6 +1745,15 @@
   </si>
   <si>
     <t>La vanne de prélèvement est-elle asservie au débit, ou au volume écoulé, et assure-t-elle un nombre de prélèvements égal, en moyenne, à au moins à 6 par heure de rejet effectif ? soit 144 prélèvements unitaires par 24h de rejet.</t>
+  </si>
+  <si>
+    <t>LISTE_7</t>
+  </si>
+  <si>
+    <t>Entre 10 et 20%</t>
+  </si>
+  <si>
+    <t>Non validé (&gt;20%)</t>
   </si>
 </sst>
 </file>
@@ -2168,7 +2178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="93">
+  <borders count="92">
     <border>
       <left/>
       <right/>
@@ -3275,19 +3285,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -3337,7 +3334,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3727,9 +3724,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3753,15 +3747,15 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="90" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="91" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="92" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3807,9 +3801,6 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="76" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3819,8 +3810,92 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -3830,6 +3905,95 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3856,187 +4020,14 @@
     <xf numFmtId="0" fontId="35" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4494,9 +4485,9 @@
     <col min="1" max="2" width="2.703125" style="68" customWidth="1"/>
     <col min="3" max="18" width="10.703125" style="68"/>
     <col min="19" max="19" width="2.703125" style="68" customWidth="1"/>
-    <col min="20" max="20" width="2.703125" style="229" customWidth="1"/>
-    <col min="21" max="21" width="10.703125" style="230"/>
-    <col min="22" max="28" width="10.703125" style="229"/>
+    <col min="20" max="20" width="2.703125" style="164" customWidth="1"/>
+    <col min="21" max="21" width="10.703125" style="165"/>
+    <col min="22" max="28" width="10.703125" style="164"/>
     <col min="29" max="16384" width="10.703125" style="68"/>
   </cols>
   <sheetData>
@@ -4522,131 +4513,131 @@
     </row>
     <row r="2" spans="2:19" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="69"/>
-      <c r="C2" s="221" t="s">
+      <c r="C2" s="171" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="222"/>
-      <c r="J2" s="222"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="222"/>
-      <c r="M2" s="222"/>
-      <c r="N2" s="222"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="223"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="173"/>
       <c r="S2" s="70"/>
     </row>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="69"/>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="174" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="216"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
-      <c r="G3" s="215"/>
-      <c r="H3" s="216" t="s">
+      <c r="D3" s="175"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="175" t="s">
         <v>201</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="215"/>
-      <c r="M3" s="216" t="s">
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="175" t="s">
         <v>205</v>
       </c>
-      <c r="N3" s="216"/>
-      <c r="O3" s="216"/>
-      <c r="P3" s="219"/>
-      <c r="Q3" s="219"/>
-      <c r="R3" s="220"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="169"/>
+      <c r="Q3" s="169"/>
+      <c r="R3" s="170"/>
       <c r="S3" s="70"/>
     </row>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="69"/>
-      <c r="C4" s="224" t="s">
+      <c r="C4" s="174" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="216"/>
-      <c r="E4" s="215"/>
-      <c r="F4" s="215"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="216" t="s">
+      <c r="D4" s="175"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="175" t="s">
         <v>202</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="216" t="s">
+      <c r="I4" s="175"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="175" t="s">
         <v>194</v>
       </c>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="219"/>
-      <c r="Q4" s="219"/>
-      <c r="R4" s="220"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="170"/>
       <c r="S4" s="70"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="69"/>
-      <c r="C5" s="224" t="s">
+      <c r="C5" s="174" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="216"/>
-      <c r="E5" s="215"/>
-      <c r="F5" s="215"/>
-      <c r="G5" s="215"/>
-      <c r="H5" s="216" t="s">
+      <c r="D5" s="175"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="216"/>
-      <c r="J5" s="215"/>
-      <c r="K5" s="215"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="216" t="s">
+      <c r="I5" s="175"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="175" t="s">
         <v>206</v>
       </c>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="217"/>
-      <c r="Q5" s="217"/>
-      <c r="R5" s="218"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="179"/>
+      <c r="R5" s="180"/>
       <c r="S5" s="70"/>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="69"/>
-      <c r="C6" s="212" t="s">
+      <c r="C6" s="181" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="213"/>
-      <c r="E6" s="214"/>
-      <c r="F6" s="214"/>
-      <c r="G6" s="214"/>
-      <c r="H6" s="213" t="s">
+      <c r="D6" s="182"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="182" t="s">
         <v>204</v>
       </c>
-      <c r="I6" s="213"/>
-      <c r="J6" s="214" t="str">
+      <c r="I6" s="182"/>
+      <c r="J6" s="183" t="str">
         <f>D25</f>
         <v>Pluviomètre</v>
       </c>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="213" t="s">
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="182" t="s">
         <v>207</v>
       </c>
-      <c r="N6" s="213"/>
-      <c r="O6" s="213"/>
-      <c r="P6" s="225"/>
-      <c r="Q6" s="225"/>
-      <c r="R6" s="226"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="182"/>
+      <c r="P6" s="177"/>
+      <c r="Q6" s="177"/>
+      <c r="R6" s="178"/>
       <c r="S6" s="70"/>
     </row>
     <row r="7" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -4671,24 +4662,24 @@
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="69"/>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="184" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="184"/>
-      <c r="E8" s="184"/>
-      <c r="F8" s="184"/>
-      <c r="G8" s="184"/>
-      <c r="H8" s="184"/>
-      <c r="I8" s="184"/>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="184"/>
-      <c r="Q8" s="184"/>
-      <c r="R8" s="185"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="185"/>
+      <c r="F8" s="185"/>
+      <c r="G8" s="185"/>
+      <c r="H8" s="185"/>
+      <c r="I8" s="185"/>
+      <c r="J8" s="185"/>
+      <c r="K8" s="185"/>
+      <c r="L8" s="185"/>
+      <c r="M8" s="185"/>
+      <c r="N8" s="185"/>
+      <c r="O8" s="185"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="185"/>
+      <c r="R8" s="186"/>
       <c r="S8" s="70"/>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -4714,118 +4705,118 @@
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="69"/>
       <c r="C10" s="63"/>
-      <c r="D10" s="198" t="s">
+      <c r="D10" s="187" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="199"/>
-      <c r="F10" s="199"/>
-      <c r="G10" s="199"/>
-      <c r="H10" s="199"/>
-      <c r="I10" s="199"/>
-      <c r="J10" s="199"/>
-      <c r="K10" s="199"/>
-      <c r="L10" s="199"/>
-      <c r="M10" s="199"/>
-      <c r="N10" s="199"/>
-      <c r="O10" s="199"/>
-      <c r="P10" s="199"/>
-      <c r="Q10" s="200"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="188"/>
+      <c r="G10" s="188"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="188"/>
+      <c r="L10" s="188"/>
+      <c r="M10" s="188"/>
+      <c r="N10" s="188"/>
+      <c r="O10" s="188"/>
+      <c r="P10" s="188"/>
+      <c r="Q10" s="189"/>
       <c r="R10" s="64"/>
       <c r="S10" s="70"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="69"/>
       <c r="C11" s="77"/>
-      <c r="D11" s="167" t="s">
+      <c r="D11" s="190" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="168"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="209"/>
-      <c r="H11" s="210"/>
-      <c r="I11" s="210"/>
-      <c r="J11" s="211"/>
-      <c r="K11" s="167" t="s">
+      <c r="E11" s="191"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="190" t="s">
         <v>211</v>
       </c>
-      <c r="L11" s="168"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="209"/>
-      <c r="O11" s="210"/>
-      <c r="P11" s="210"/>
-      <c r="Q11" s="211"/>
+      <c r="L11" s="191"/>
+      <c r="M11" s="192"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="167"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="168"/>
       <c r="R11" s="78"/>
       <c r="S11" s="70"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="69"/>
       <c r="C12" s="77"/>
-      <c r="D12" s="167" t="s">
+      <c r="D12" s="190" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="168"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="209"/>
-      <c r="H12" s="210"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="211"/>
-      <c r="K12" s="167" t="s">
+      <c r="E12" s="191"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="166"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="190" t="s">
         <v>212</v>
       </c>
-      <c r="L12" s="168"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="209"/>
-      <c r="O12" s="210"/>
-      <c r="P12" s="210"/>
-      <c r="Q12" s="211"/>
+      <c r="L12" s="191"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="166"/>
+      <c r="O12" s="167"/>
+      <c r="P12" s="167"/>
+      <c r="Q12" s="168"/>
       <c r="R12" s="78"/>
       <c r="S12" s="70"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="69"/>
       <c r="C13" s="77"/>
-      <c r="D13" s="167" t="s">
+      <c r="D13" s="190" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="168"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="209"/>
-      <c r="H13" s="210"/>
-      <c r="I13" s="210"/>
-      <c r="J13" s="211"/>
-      <c r="K13" s="167" t="s">
+      <c r="E13" s="191"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="167"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="190" t="s">
         <v>213</v>
       </c>
-      <c r="L13" s="168"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="209"/>
-      <c r="O13" s="210"/>
-      <c r="P13" s="210"/>
-      <c r="Q13" s="211"/>
+      <c r="L13" s="191"/>
+      <c r="M13" s="192"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="167"/>
+      <c r="P13" s="167"/>
+      <c r="Q13" s="168"/>
       <c r="R13" s="78"/>
       <c r="S13" s="70"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="69"/>
       <c r="C14" s="77"/>
-      <c r="D14" s="167" t="s">
+      <c r="D14" s="190" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="168"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="209"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="210"/>
-      <c r="J14" s="211"/>
-      <c r="K14" s="167" t="s">
+      <c r="E14" s="191"/>
+      <c r="F14" s="192"/>
+      <c r="G14" s="166"/>
+      <c r="H14" s="167"/>
+      <c r="I14" s="167"/>
+      <c r="J14" s="168"/>
+      <c r="K14" s="190" t="s">
         <v>214</v>
       </c>
-      <c r="L14" s="168"/>
-      <c r="M14" s="169"/>
-      <c r="N14" s="209"/>
-      <c r="O14" s="210"/>
-      <c r="P14" s="210"/>
-      <c r="Q14" s="211"/>
+      <c r="L14" s="191"/>
+      <c r="M14" s="192"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="167"/>
+      <c r="P14" s="167"/>
+      <c r="Q14" s="168"/>
       <c r="R14" s="78"/>
       <c r="S14" s="70"/>
     </row>
@@ -4839,15 +4830,15 @@
       <c r="H15" s="89"/>
       <c r="I15" s="89"/>
       <c r="J15" s="89"/>
-      <c r="K15" s="167" t="s">
+      <c r="K15" s="190" t="s">
         <v>231</v>
       </c>
-      <c r="L15" s="168"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="171"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="172"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="192"/>
+      <c r="N15" s="219"/>
+      <c r="O15" s="220"/>
+      <c r="P15" s="220"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="78"/>
       <c r="S15" s="70"/>
     </row>
@@ -4874,14 +4865,14 @@
     <row r="17" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B17" s="69"/>
       <c r="C17" s="77"/>
-      <c r="D17" s="198" t="s">
+      <c r="D17" s="187" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="199"/>
-      <c r="F17" s="199"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="199"/>
-      <c r="I17" s="200"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="188"/>
+      <c r="H17" s="188"/>
+      <c r="I17" s="189"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -4896,18 +4887,18 @@
     <row r="18" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="69"/>
       <c r="C18" s="77"/>
-      <c r="D18" s="204" t="s">
+      <c r="D18" s="200" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="204"/>
-      <c r="F18" s="205" t="s">
+      <c r="E18" s="200"/>
+      <c r="F18" s="201" t="s">
         <v>178</v>
       </c>
-      <c r="G18" s="205"/>
-      <c r="H18" s="206" t="s">
+      <c r="G18" s="201"/>
+      <c r="H18" s="202" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="206"/>
+      <c r="I18" s="202"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -4922,15 +4913,15 @@
     <row r="19" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="77"/>
-      <c r="D19" s="207"/>
-      <c r="E19" s="207"/>
-      <c r="F19" s="207"/>
-      <c r="G19" s="207"/>
-      <c r="H19" s="208" t="str">
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="204" t="str">
         <f>IF(D19&gt;0,D19-F19,"-")</f>
         <v>-</v>
       </c>
-      <c r="I19" s="208"/>
+      <c r="I19" s="204"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -4941,7 +4932,7 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="78"/>
       <c r="S19" s="70"/>
-      <c r="U19" s="230">
+      <c r="U19" s="165">
         <f>IF(H19&lt;&gt;"-",IF(ABS(H19)&gt;1, 1,0),-1)</f>
         <v>-1</v>
       </c>
@@ -4949,15 +4940,15 @@
     <row r="20" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="69"/>
       <c r="C20" s="77"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="201"/>
-      <c r="G20" s="201"/>
-      <c r="H20" s="202" t="str">
+      <c r="D20" s="197"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="197"/>
+      <c r="G20" s="197"/>
+      <c r="H20" s="198" t="str">
         <f>IF(D20&gt;0,D20-F20,"-")</f>
         <v>-</v>
       </c>
-      <c r="I20" s="202"/>
+      <c r="I20" s="198"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -4968,7 +4959,7 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="78"/>
       <c r="S20" s="70"/>
-      <c r="U20" s="230">
+      <c r="U20" s="165">
         <f>IF(H20&lt;&gt;"-",IF(ABS(H20)&gt;1, 1,0),-1)</f>
         <v>-1</v>
       </c>
@@ -4992,7 +4983,7 @@
       <c r="Q21" s="80"/>
       <c r="R21" s="81"/>
       <c r="S21" s="70"/>
-      <c r="U21" s="230" t="str">
+      <c r="U21" s="165" t="str">
         <f>IF(MAX(U19:U20)&gt;-1,IF(MAX(U19:U20)=1,"Non validé","Validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -5019,24 +5010,24 @@
     </row>
     <row r="23" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B23" s="69"/>
-      <c r="C23" s="183" t="s">
+      <c r="C23" s="184" t="s">
         <v>216</v>
       </c>
-      <c r="D23" s="184"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="184"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="184"/>
-      <c r="J23" s="184"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="184"/>
-      <c r="M23" s="184"/>
-      <c r="N23" s="184"/>
-      <c r="O23" s="184"/>
-      <c r="P23" s="184"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="185"/>
+      <c r="D23" s="185"/>
+      <c r="E23" s="185"/>
+      <c r="F23" s="185"/>
+      <c r="G23" s="185"/>
+      <c r="H23" s="185"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="185"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="185"/>
+      <c r="Q23" s="185"/>
+      <c r="R23" s="186"/>
       <c r="S23" s="70"/>
     </row>
     <row r="24" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5062,46 +5053,46 @@
     <row r="25" spans="2:21" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B25" s="69"/>
       <c r="C25" s="63"/>
-      <c r="D25" s="203" t="s">
+      <c r="D25" s="199" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="203"/>
-      <c r="H25" s="203"/>
-      <c r="I25" s="203"/>
-      <c r="J25" s="203"/>
-      <c r="K25" s="203"/>
-      <c r="L25" s="203"/>
-      <c r="M25" s="203"/>
-      <c r="N25" s="203"/>
-      <c r="O25" s="203"/>
-      <c r="P25" s="203"/>
-      <c r="Q25" s="203"/>
+      <c r="E25" s="199"/>
+      <c r="F25" s="199"/>
+      <c r="G25" s="199"/>
+      <c r="H25" s="199"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="199"/>
+      <c r="L25" s="199"/>
+      <c r="M25" s="199"/>
+      <c r="N25" s="199"/>
+      <c r="O25" s="199"/>
+      <c r="P25" s="199"/>
+      <c r="Q25" s="199"/>
       <c r="R25" s="64"/>
       <c r="S25" s="70"/>
     </row>
     <row r="26" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="69"/>
       <c r="C26" s="63"/>
-      <c r="D26" s="194" t="s">
+      <c r="D26" s="193" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="195"/>
-      <c r="F26" s="195"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="195"/>
-      <c r="I26" s="196"/>
-      <c r="J26" s="194" t="s">
+      <c r="E26" s="194"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="194"/>
+      <c r="H26" s="194"/>
+      <c r="I26" s="195"/>
+      <c r="J26" s="193" t="s">
         <v>174</v>
       </c>
-      <c r="K26" s="195"/>
-      <c r="L26" s="195"/>
-      <c r="M26" s="196"/>
-      <c r="N26" s="197" t="s">
+      <c r="K26" s="194"/>
+      <c r="L26" s="194"/>
+      <c r="M26" s="195"/>
+      <c r="N26" s="196" t="s">
         <v>75</v>
       </c>
-      <c r="O26" s="197"/>
+      <c r="O26" s="196"/>
       <c r="P26" s="82" t="s">
         <v>189</v>
       </c>
@@ -5110,7 +5101,7 @@
       </c>
       <c r="R26" s="64"/>
       <c r="S26" s="70"/>
-      <c r="U26" s="230" t="s">
+      <c r="U26" s="165" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5120,23 +5111,23 @@
       <c r="D27" s="83">
         <v>1</v>
       </c>
-      <c r="E27" s="177" t="str">
+      <c r="E27" s="213" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D27+2,FALSE),"")</f>
         <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
       </c>
-      <c r="F27" s="178"/>
-      <c r="G27" s="178"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="178"/>
-      <c r="J27" s="177" t="str">
+      <c r="F27" s="214"/>
+      <c r="G27" s="214"/>
+      <c r="H27" s="214"/>
+      <c r="I27" s="214"/>
+      <c r="J27" s="213" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D27+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
       </c>
-      <c r="K27" s="178"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="179"/>
-      <c r="N27" s="180"/>
-      <c r="O27" s="181"/>
+      <c r="K27" s="214"/>
+      <c r="L27" s="214"/>
+      <c r="M27" s="215"/>
+      <c r="N27" s="216"/>
+      <c r="O27" s="217"/>
       <c r="P27" s="84">
         <f>IF(OR(N27="Validé",N27="Réserve",N27="Oui"),Q27,0)</f>
         <v>0</v>
@@ -5147,7 +5138,7 @@
       </c>
       <c r="R27" s="64"/>
       <c r="S27" s="70"/>
-      <c r="U27" s="230" t="s">
+      <c r="U27" s="165" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5157,26 +5148,26 @@
       <c r="D28" s="83">
         <v>2</v>
       </c>
-      <c r="E28" s="177" t="str">
+      <c r="E28" s="213" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D28+2,FALSE),"")</f>
         <v>Le pluviomètre présente t-il une section suffisante ?</v>
       </c>
-      <c r="F28" s="178"/>
-      <c r="G28" s="178"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="177" t="str">
+      <c r="F28" s="214"/>
+      <c r="G28" s="214"/>
+      <c r="H28" s="214"/>
+      <c r="I28" s="214"/>
+      <c r="J28" s="213" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D28+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Entre 180 et 1 000 cm2, soit un diamètre variant entre 15 et 35 cm.</v>
       </c>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="179"/>
-      <c r="N28" s="180" t="str">
+      <c r="K28" s="214"/>
+      <c r="L28" s="214"/>
+      <c r="M28" s="215"/>
+      <c r="N28" s="216" t="str">
         <f>IF(N13&lt;&gt;"",IF(AND(N13&gt;=15,N13&lt;=35),"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O28" s="181"/>
+      <c r="O28" s="217"/>
       <c r="P28" s="84">
         <f t="shared" ref="P28:P31" si="0">IF(OR(N28="Validé",N28="Réserve",N28="Oui"),Q28,0)</f>
         <v>0</v>
@@ -5187,7 +5178,7 @@
       </c>
       <c r="R28" s="64"/>
       <c r="S28" s="70"/>
-      <c r="U28" s="230" t="s">
+      <c r="U28" s="165" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5197,23 +5188,23 @@
       <c r="D29" s="83">
         <v>3</v>
       </c>
-      <c r="E29" s="177" t="str">
+      <c r="E29" s="213" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D29+2,FALSE),"")</f>
         <v>Le pluviomètre est-il installé conformément aux règles de l'art et/ou aux prescriptions des constructeurs ?</v>
       </c>
-      <c r="F29" s="178"/>
-      <c r="G29" s="178"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="178"/>
-      <c r="J29" s="177" t="str">
+      <c r="F29" s="214"/>
+      <c r="G29" s="214"/>
+      <c r="H29" s="214"/>
+      <c r="I29" s="214"/>
+      <c r="J29" s="213" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D29+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Sur une surface horizontale, entre 0,5 et 2 mètres du sol (1 mètre recommandé), à une distance supérieure à 4 fois la hauteur d'obstacles (mur, arbres, etc…).</v>
       </c>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="179"/>
-      <c r="N29" s="180"/>
-      <c r="O29" s="181"/>
+      <c r="K29" s="214"/>
+      <c r="L29" s="214"/>
+      <c r="M29" s="215"/>
+      <c r="N29" s="216"/>
+      <c r="O29" s="217"/>
       <c r="P29" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5224,7 +5215,7 @@
       </c>
       <c r="R29" s="64"/>
       <c r="S29" s="70"/>
-      <c r="U29" s="230" t="s">
+      <c r="U29" s="165" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5234,24 +5225,24 @@
       <c r="D30" s="83">
         <v>4</v>
       </c>
-      <c r="E30" s="177" t="str">
+      <c r="E30" s="213" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D30+2,FALSE),"")</f>
         <v>La propreté et l'état d'entretien du pluviomètre, sont-ils satisfaisants ?</v>
       </c>
-      <c r="F30" s="178"/>
-      <c r="G30" s="178"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="177" t="str">
+      <c r="F30" s="214"/>
+      <c r="G30" s="214"/>
+      <c r="H30" s="214"/>
+      <c r="I30" s="214"/>
+      <c r="J30" s="213" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D30+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
 Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
       </c>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="179"/>
-      <c r="N30" s="180"/>
-      <c r="O30" s="181"/>
+      <c r="K30" s="214"/>
+      <c r="L30" s="214"/>
+      <c r="M30" s="215"/>
+      <c r="N30" s="216"/>
+      <c r="O30" s="217"/>
       <c r="P30" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5262,7 +5253,7 @@
       </c>
       <c r="R30" s="64"/>
       <c r="S30" s="70"/>
-      <c r="U30" s="230" t="s">
+      <c r="U30" s="165" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5272,26 +5263,26 @@
       <c r="D31" s="83">
         <v>5</v>
       </c>
-      <c r="E31" s="177" t="str">
+      <c r="E31" s="213" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D31+2,FALSE),"")</f>
         <v>L'écart entre d'une part la mesure de la hauteur de pluie réalisée à partir du dispositif en place et celle réalisée par l'organisme de contrôle d'autre part, est-il cohérent (EMT ± 1 unité) ?</v>
       </c>
-      <c r="F31" s="178"/>
-      <c r="G31" s="178"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="177" t="str">
+      <c r="F31" s="214"/>
+      <c r="G31" s="214"/>
+      <c r="H31" s="214"/>
+      <c r="I31" s="214"/>
+      <c r="J31" s="213" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D31+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>-</v>
       </c>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="179"/>
-      <c r="N31" s="180" t="str">
+      <c r="K31" s="214"/>
+      <c r="L31" s="214"/>
+      <c r="M31" s="215"/>
+      <c r="N31" s="216" t="str">
         <f>U21</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O31" s="181"/>
+      <c r="O31" s="217"/>
       <c r="P31" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5302,57 +5293,57 @@
       </c>
       <c r="R31" s="64"/>
       <c r="S31" s="70"/>
-      <c r="U31" s="230" t="s">
+      <c r="U31" s="165" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="69"/>
       <c r="C32" s="63"/>
-      <c r="D32" s="193" t="s">
+      <c r="D32" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="193"/>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="193"/>
-      <c r="L32" s="193"/>
-      <c r="M32" s="193"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="182" t="s">
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="218"/>
+      <c r="H32" s="218"/>
+      <c r="I32" s="218"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="218"/>
+      <c r="L32" s="218"/>
+      <c r="M32" s="218"/>
+      <c r="N32" s="212"/>
+      <c r="O32" s="212"/>
+      <c r="P32" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="Q32" s="182"/>
+      <c r="Q32" s="212"/>
       <c r="R32" s="64"/>
       <c r="S32" s="70"/>
     </row>
     <row r="33" spans="2:19" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="69"/>
       <c r="C33" s="63"/>
-      <c r="D33" s="173"/>
-      <c r="E33" s="173"/>
-      <c r="F33" s="173"/>
-      <c r="G33" s="173"/>
-      <c r="H33" s="173"/>
-      <c r="I33" s="173"/>
-      <c r="J33" s="173"/>
-      <c r="K33" s="173"/>
-      <c r="L33" s="173"/>
-      <c r="M33" s="173"/>
-      <c r="N33" s="174" t="str">
+      <c r="D33" s="222"/>
+      <c r="E33" s="222"/>
+      <c r="F33" s="222"/>
+      <c r="G33" s="222"/>
+      <c r="H33" s="222"/>
+      <c r="I33" s="222"/>
+      <c r="J33" s="222"/>
+      <c r="K33" s="222"/>
+      <c r="L33" s="222"/>
+      <c r="M33" s="222"/>
+      <c r="N33" s="223" t="str">
         <f>IF(P33&gt;80,"Validé",IF(P33&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O33" s="174"/>
-      <c r="P33" s="175">
+      <c r="O33" s="223"/>
+      <c r="P33" s="224">
         <f>IF(SUM(P27:P31)&gt;100,100,SUM(P27:P31))</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="176"/>
+      <c r="Q33" s="225"/>
       <c r="R33" s="64"/>
       <c r="S33" s="70"/>
     </row>
@@ -5398,124 +5389,124 @@
     </row>
     <row r="36" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="69"/>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="184" t="s">
         <v>217</v>
       </c>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
-      <c r="O36" s="184"/>
-      <c r="P36" s="184"/>
-      <c r="Q36" s="184"/>
-      <c r="R36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="185"/>
+      <c r="M36" s="185"/>
+      <c r="N36" s="185"/>
+      <c r="O36" s="185"/>
+      <c r="P36" s="185"/>
+      <c r="Q36" s="185"/>
+      <c r="R36" s="186"/>
       <c r="S36" s="70"/>
     </row>
     <row r="37" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B37" s="69"/>
-      <c r="C37" s="186"/>
-      <c r="D37" s="187"/>
-      <c r="E37" s="187"/>
-      <c r="F37" s="187"/>
-      <c r="G37" s="187"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="187"/>
-      <c r="J37" s="187"/>
-      <c r="K37" s="187"/>
-      <c r="L37" s="187"/>
-      <c r="M37" s="187"/>
-      <c r="N37" s="187"/>
-      <c r="O37" s="187"/>
-      <c r="P37" s="187"/>
-      <c r="Q37" s="187"/>
-      <c r="R37" s="188"/>
+      <c r="C37" s="205"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="206"/>
+      <c r="F37" s="206"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="206"/>
+      <c r="I37" s="206"/>
+      <c r="J37" s="206"/>
+      <c r="K37" s="206"/>
+      <c r="L37" s="206"/>
+      <c r="M37" s="206"/>
+      <c r="N37" s="206"/>
+      <c r="O37" s="206"/>
+      <c r="P37" s="206"/>
+      <c r="Q37" s="206"/>
+      <c r="R37" s="207"/>
       <c r="S37" s="70"/>
     </row>
     <row r="38" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="69"/>
-      <c r="C38" s="189"/>
-      <c r="D38" s="187"/>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187"/>
-      <c r="G38" s="187"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="187"/>
-      <c r="L38" s="187"/>
-      <c r="M38" s="187"/>
-      <c r="N38" s="187"/>
-      <c r="O38" s="187"/>
-      <c r="P38" s="187"/>
-      <c r="Q38" s="187"/>
-      <c r="R38" s="188"/>
+      <c r="C38" s="208"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="206"/>
+      <c r="I38" s="206"/>
+      <c r="J38" s="206"/>
+      <c r="K38" s="206"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="206"/>
+      <c r="O38" s="206"/>
+      <c r="P38" s="206"/>
+      <c r="Q38" s="206"/>
+      <c r="R38" s="207"/>
       <c r="S38" s="70"/>
     </row>
     <row r="39" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="69"/>
-      <c r="C39" s="189"/>
-      <c r="D39" s="187"/>
-      <c r="E39" s="187"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="187"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="187"/>
-      <c r="J39" s="187"/>
-      <c r="K39" s="187"/>
-      <c r="L39" s="187"/>
-      <c r="M39" s="187"/>
-      <c r="N39" s="187"/>
-      <c r="O39" s="187"/>
-      <c r="P39" s="187"/>
-      <c r="Q39" s="187"/>
-      <c r="R39" s="188"/>
+      <c r="C39" s="208"/>
+      <c r="D39" s="206"/>
+      <c r="E39" s="206"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="206"/>
+      <c r="I39" s="206"/>
+      <c r="J39" s="206"/>
+      <c r="K39" s="206"/>
+      <c r="L39" s="206"/>
+      <c r="M39" s="206"/>
+      <c r="N39" s="206"/>
+      <c r="O39" s="206"/>
+      <c r="P39" s="206"/>
+      <c r="Q39" s="206"/>
+      <c r="R39" s="207"/>
       <c r="S39" s="70"/>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="69"/>
-      <c r="C40" s="189"/>
-      <c r="D40" s="187"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="187"/>
-      <c r="H40" s="187"/>
-      <c r="I40" s="187"/>
-      <c r="J40" s="187"/>
-      <c r="K40" s="187"/>
-      <c r="L40" s="187"/>
-      <c r="M40" s="187"/>
-      <c r="N40" s="187"/>
-      <c r="O40" s="187"/>
-      <c r="P40" s="187"/>
-      <c r="Q40" s="187"/>
-      <c r="R40" s="188"/>
+      <c r="C40" s="208"/>
+      <c r="D40" s="206"/>
+      <c r="E40" s="206"/>
+      <c r="F40" s="206"/>
+      <c r="G40" s="206"/>
+      <c r="H40" s="206"/>
+      <c r="I40" s="206"/>
+      <c r="J40" s="206"/>
+      <c r="K40" s="206"/>
+      <c r="L40" s="206"/>
+      <c r="M40" s="206"/>
+      <c r="N40" s="206"/>
+      <c r="O40" s="206"/>
+      <c r="P40" s="206"/>
+      <c r="Q40" s="206"/>
+      <c r="R40" s="207"/>
       <c r="S40" s="70"/>
     </row>
     <row r="41" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B41" s="69"/>
-      <c r="C41" s="190"/>
-      <c r="D41" s="191"/>
-      <c r="E41" s="191"/>
-      <c r="F41" s="191"/>
-      <c r="G41" s="191"/>
-      <c r="H41" s="191"/>
-      <c r="I41" s="191"/>
-      <c r="J41" s="191"/>
-      <c r="K41" s="191"/>
-      <c r="L41" s="191"/>
-      <c r="M41" s="191"/>
-      <c r="N41" s="191"/>
-      <c r="O41" s="191"/>
-      <c r="P41" s="191"/>
-      <c r="Q41" s="191"/>
-      <c r="R41" s="192"/>
+      <c r="C41" s="209"/>
+      <c r="D41" s="210"/>
+      <c r="E41" s="210"/>
+      <c r="F41" s="210"/>
+      <c r="G41" s="210"/>
+      <c r="H41" s="210"/>
+      <c r="I41" s="210"/>
+      <c r="J41" s="210"/>
+      <c r="K41" s="210"/>
+      <c r="L41" s="210"/>
+      <c r="M41" s="210"/>
+      <c r="N41" s="210"/>
+      <c r="O41" s="210"/>
+      <c r="P41" s="210"/>
+      <c r="Q41" s="210"/>
+      <c r="R41" s="211"/>
       <c r="S41" s="70"/>
     </row>
     <row r="42" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5539,8 +5530,75 @@
       <c r="S42" s="73"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p09Hq+XQQKrM8zU2Qm9C/+AKxmp1Pqk74JkhsGgwxHk6VCqgbyQ9YfW6JBoA7gbT9WEEZtz4rUcO98IzPiEk3A==" saltValue="JT5b4JufFoRK9JcMuiYtZA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Wc9AwwZGrSXNoq0x7LZfwq727AgMT+WcTTreH3X1mWNJkimZ2wMXkI5ISY3Xdn1/hG76ggf9nbYSQbyVVRDgIw==" saltValue="1nzoJxCNJFTEFDhb9WkWfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="83">
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="D33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="C36:R36"/>
+    <mergeCell ref="C37:R41"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="D32:M32"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C23:R23"/>
+    <mergeCell ref="D25:Q25"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="C8:R8"/>
+    <mergeCell ref="D10:Q10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="N13:Q13"/>
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="C2:R2"/>
@@ -5557,73 +5615,6 @@
     <mergeCell ref="M4:O4"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="C8:R8"/>
-    <mergeCell ref="D10:Q10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C23:R23"/>
-    <mergeCell ref="D25:Q25"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C36:R36"/>
-    <mergeCell ref="C37:R41"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="D32:M32"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="D33:M33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="N32:O32"/>
   </mergeCells>
   <conditionalFormatting sqref="H19:I19">
     <cfRule type="expression" dxfId="14" priority="13">
@@ -6284,91 +6275,91 @@
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:603" ht="37.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="147"/>
-      <c r="B2" s="148" t="s">
+      <c r="A2" s="146"/>
+      <c r="B2" s="147" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="150"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="151"/>
-      <c r="R2" s="150"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="152" t="s">
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="150"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="149"/>
+      <c r="S2" s="149"/>
+      <c r="T2" s="150"/>
+      <c r="U2" s="150"/>
+      <c r="V2" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="W2" s="153"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="153"/>
-      <c r="AE2" s="153"/>
-      <c r="AF2" s="154"/>
-      <c r="AG2" s="154"/>
-      <c r="AH2" s="153"/>
-      <c r="AI2" s="153"/>
-      <c r="AJ2" s="154"/>
-      <c r="AK2" s="154"/>
-      <c r="AL2" s="153"/>
-      <c r="AM2" s="153"/>
-      <c r="AN2" s="154"/>
-      <c r="AO2" s="154"/>
-      <c r="AP2" s="153"/>
-      <c r="AQ2" s="153"/>
-      <c r="AR2" s="154"/>
-      <c r="AS2" s="154"/>
-      <c r="AT2" s="153"/>
-      <c r="AU2" s="153"/>
-      <c r="AV2" s="154"/>
-      <c r="AW2" s="154"/>
-      <c r="AX2" s="153"/>
-      <c r="AY2" s="153"/>
-      <c r="AZ2" s="154"/>
-      <c r="BA2" s="154"/>
-      <c r="BB2" s="153"/>
-      <c r="BC2" s="153"/>
-      <c r="BD2" s="154"/>
-      <c r="BE2" s="154"/>
-      <c r="BF2" s="155" t="s">
+      <c r="W2" s="152"/>
+      <c r="X2" s="153"/>
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="153"/>
+      <c r="AC2" s="153"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="152"/>
+      <c r="AF2" s="153"/>
+      <c r="AG2" s="153"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="153"/>
+      <c r="AK2" s="153"/>
+      <c r="AL2" s="152"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="153"/>
+      <c r="AO2" s="153"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="153"/>
+      <c r="AT2" s="152"/>
+      <c r="AU2" s="152"/>
+      <c r="AV2" s="153"/>
+      <c r="AW2" s="153"/>
+      <c r="AX2" s="152"/>
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="153"/>
+      <c r="BA2" s="153"/>
+      <c r="BB2" s="152"/>
+      <c r="BC2" s="152"/>
+      <c r="BD2" s="153"/>
+      <c r="BE2" s="153"/>
+      <c r="BF2" s="154" t="s">
         <v>301</v>
       </c>
-      <c r="BG2" s="156"/>
-      <c r="BH2" s="156"/>
-      <c r="BI2" s="156"/>
-      <c r="BJ2" s="156"/>
-      <c r="BK2" s="156"/>
-      <c r="BL2" s="156"/>
-      <c r="BM2" s="156"/>
-      <c r="BN2" s="156"/>
-      <c r="BO2" s="156"/>
-      <c r="BP2" s="156"/>
-      <c r="BQ2" s="156"/>
-      <c r="BR2" s="157" t="s">
+      <c r="BG2" s="155"/>
+      <c r="BH2" s="155"/>
+      <c r="BI2" s="155"/>
+      <c r="BJ2" s="155"/>
+      <c r="BK2" s="155"/>
+      <c r="BL2" s="155"/>
+      <c r="BM2" s="155"/>
+      <c r="BN2" s="155"/>
+      <c r="BO2" s="155"/>
+      <c r="BP2" s="155"/>
+      <c r="BQ2" s="155"/>
+      <c r="BR2" s="156" t="s">
         <v>302</v>
       </c>
-      <c r="BS2" s="158"/>
-      <c r="BT2" s="158"/>
-      <c r="BU2" s="158"/>
-      <c r="BV2" s="158"/>
-      <c r="BW2" s="158"/>
-      <c r="BX2" s="158"/>
-      <c r="BY2" s="158"/>
+      <c r="BS2" s="157"/>
+      <c r="BT2" s="157"/>
+      <c r="BU2" s="157"/>
+      <c r="BV2" s="157"/>
+      <c r="BW2" s="157"/>
+      <c r="BX2" s="157"/>
+      <c r="BY2" s="157"/>
       <c r="LK2" s="19"/>
       <c r="MD2" s="19"/>
       <c r="MT2" s="19"/>
@@ -7319,7 +7310,7 @@
         <v>10</v>
       </c>
       <c r="AK7" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL7" s="24" t="s">
         <v>124</v>
@@ -7329,7 +7320,7 @@
         <v>10</v>
       </c>
       <c r="AO7" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP7" s="24" t="s">
         <v>125</v>
@@ -7365,7 +7356,7 @@
         <v>10</v>
       </c>
       <c r="BA7" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB7" s="24" t="s">
         <v>128</v>
@@ -7377,7 +7368,7 @@
         <v>20</v>
       </c>
       <c r="BE7" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BF7" s="24" t="s">
         <v>129</v>
@@ -7466,7 +7457,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="J8" s="40" t="s">
         <v>132</v>
@@ -7598,7 +7589,7 @@
         <v>10</v>
       </c>
       <c r="BA8" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB8" s="40" t="s">
         <v>137</v>
@@ -7685,7 +7676,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="124" t="s">
         <v>141</v>
@@ -7697,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="124" t="s">
         <v>139</v>
@@ -7709,7 +7700,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9" s="124" t="s">
         <v>139</v>
@@ -7721,7 +7712,7 @@
         <v>20</v>
       </c>
       <c r="Q9" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R9" s="124" t="s">
         <v>139</v>
@@ -7733,7 +7724,7 @@
         <v>20</v>
       </c>
       <c r="U9" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V9" s="10" t="s">
         <v>34</v>
@@ -7853,7 +7844,7 @@
         <v>5</v>
       </c>
       <c r="BI9" s="121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ9" s="122" t="s">
         <v>148</v>
@@ -7865,7 +7856,7 @@
         <v>5</v>
       </c>
       <c r="BM9" s="123" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BN9" s="124" t="s">
         <v>150</v>
@@ -7886,7 +7877,7 @@
         <v>233</v>
       </c>
       <c r="BT9" s="126"/>
-      <c r="BU9" s="139" t="s">
+      <c r="BU9" s="138" t="s">
         <v>234</v>
       </c>
       <c r="BV9" s="10" t="s">
@@ -7916,7 +7907,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="47" t="s">
         <v>294</v>
@@ -7928,7 +7919,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="47" t="s">
         <v>226</v>
@@ -7940,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N10" s="47" t="s">
         <v>226</v>
@@ -7952,7 +7943,7 @@
         <v>20</v>
       </c>
       <c r="Q10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R10" s="47" t="s">
         <v>226</v>
@@ -7964,7 +7955,7 @@
         <v>20</v>
       </c>
       <c r="U10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V10" s="44" t="s">
         <v>151</v>
@@ -8056,7 +8047,7 @@
         <v>20</v>
       </c>
       <c r="BA10" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB10" s="40" t="s">
         <v>154</v>
@@ -8068,7 +8059,7 @@
         <v>5</v>
       </c>
       <c r="BE10" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BF10" s="40" t="s">
         <v>35</v>
@@ -8080,7 +8071,7 @@
         <v>5</v>
       </c>
       <c r="BI10" s="96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ10" s="97" t="s">
         <v>233</v>
@@ -8101,7 +8092,7 @@
         <v>233</v>
       </c>
       <c r="BP10" s="42"/>
-      <c r="BQ10" s="140" t="s">
+      <c r="BQ10" s="139" t="s">
         <v>234</v>
       </c>
       <c r="BR10" s="44" t="s">
@@ -8121,7 +8112,7 @@
         <v>233</v>
       </c>
       <c r="BX10" s="42"/>
-      <c r="BY10" s="140" t="s">
+      <c r="BY10" s="139" t="s">
         <v>234</v>
       </c>
     </row>
@@ -8139,7 +8130,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="124" t="s">
         <v>295</v>
@@ -8151,7 +8142,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="124" t="s">
         <v>230</v>
@@ -8163,7 +8154,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N11" s="124" t="s">
         <v>230</v>
@@ -8175,7 +8166,7 @@
         <v>20</v>
       </c>
       <c r="Q11" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R11" s="124" t="s">
         <v>230</v>
@@ -8187,7 +8178,7 @@
         <v>20</v>
       </c>
       <c r="U11" s="127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V11" s="10" t="s">
         <v>156</v>
@@ -8199,7 +8190,7 @@
         <v>10</v>
       </c>
       <c r="Y11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>156</v>
@@ -8211,7 +8202,7 @@
         <v>10</v>
       </c>
       <c r="AC11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD11" s="10" t="s">
         <v>156</v>
@@ -8223,7 +8214,7 @@
         <v>10</v>
       </c>
       <c r="AG11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH11" s="10" t="s">
         <v>156</v>
@@ -8235,7 +8226,7 @@
         <v>10</v>
       </c>
       <c r="AK11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL11" s="10" t="s">
         <v>156</v>
@@ -8247,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="AO11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP11" s="10" t="s">
         <v>156</v>
@@ -8259,7 +8250,7 @@
         <v>10</v>
       </c>
       <c r="AS11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT11" s="24" t="s">
         <v>296</v>
@@ -8271,7 +8262,7 @@
         <v>15</v>
       </c>
       <c r="AW11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>157</v>
@@ -8283,7 +8274,7 @@
         <v>20</v>
       </c>
       <c r="BA11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB11" s="24" t="s">
         <v>158</v>
@@ -8295,7 +8286,7 @@
         <v>5</v>
       </c>
       <c r="BE11" s="119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BF11" s="24" t="s">
         <v>155</v>
@@ -8309,17 +8300,17 @@
       <c r="BI11" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="BJ11" s="159" t="s">
+      <c r="BJ11" s="158" t="s">
         <v>304</v>
       </c>
-      <c r="BK11" s="160" t="s">
+      <c r="BK11" s="159" t="s">
         <v>229</v>
       </c>
-      <c r="BL11" s="161">
+      <c r="BL11" s="160">
         <v>10</v>
       </c>
-      <c r="BM11" s="162" t="s">
-        <v>41</v>
+      <c r="BM11" s="123" t="s">
+        <v>40</v>
       </c>
       <c r="BN11" s="24" t="s">
         <v>233</v>
@@ -8338,7 +8329,7 @@
         <v>233</v>
       </c>
       <c r="BT11" s="118"/>
-      <c r="BU11" s="141" t="s">
+      <c r="BU11" s="140" t="s">
         <v>234</v>
       </c>
       <c r="BV11" s="10" t="s">
@@ -8366,7 +8357,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="40" t="s">
         <v>159</v>
@@ -8378,7 +8369,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" s="51" t="s">
         <v>159</v>
@@ -8390,7 +8381,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N12" s="51" t="s">
         <v>159</v>
@@ -8402,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R12" s="51" t="s">
         <v>159</v>
@@ -8414,7 +8405,7 @@
         <v>10</v>
       </c>
       <c r="U12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V12" s="44" t="s">
         <v>161</v>
@@ -8426,7 +8417,7 @@
         <v>10</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z12" s="44" t="s">
         <v>161</v>
@@ -8438,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD12" s="44" t="s">
         <v>161</v>
@@ -8450,7 +8441,7 @@
         <v>10</v>
       </c>
       <c r="AG12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>161</v>
@@ -8462,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="AK12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL12" s="44" t="s">
         <v>161</v>
@@ -8474,7 +8465,7 @@
         <v>10</v>
       </c>
       <c r="AO12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP12" s="44" t="s">
         <v>161</v>
@@ -8486,7 +8477,7 @@
         <v>10</v>
       </c>
       <c r="AS12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT12" s="40" t="s">
         <v>297</v>
@@ -8498,7 +8489,7 @@
         <v>15</v>
       </c>
       <c r="AW12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX12" s="47" t="s">
         <v>162</v>
@@ -8509,8 +8500,8 @@
       <c r="AZ12" s="49">
         <v>20</v>
       </c>
-      <c r="BA12" s="50" t="s">
-        <v>41</v>
+      <c r="BA12" s="43" t="s">
+        <v>40</v>
       </c>
       <c r="BB12" s="40" t="s">
         <v>233</v>
@@ -8532,7 +8523,7 @@
         <v>5</v>
       </c>
       <c r="BI12" s="96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ12" s="97" t="s">
         <v>36</v>
@@ -8544,7 +8535,7 @@
         <v>5</v>
       </c>
       <c r="BM12" s="98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BN12" s="40" t="s">
         <v>233</v>
@@ -8553,7 +8544,7 @@
         <v>233</v>
       </c>
       <c r="BP12" s="42"/>
-      <c r="BQ12" s="142" t="s">
+      <c r="BQ12" s="141" t="s">
         <v>234</v>
       </c>
       <c r="BR12" s="44" t="s">
@@ -8563,7 +8554,7 @@
         <v>233</v>
       </c>
       <c r="BT12" s="42"/>
-      <c r="BU12" s="140" t="s">
+      <c r="BU12" s="139" t="s">
         <v>234</v>
       </c>
       <c r="BV12" s="44" t="s">
@@ -8573,7 +8564,7 @@
         <v>233</v>
       </c>
       <c r="BX12" s="42"/>
-      <c r="BY12" s="143" t="s">
+      <c r="BY12" s="142" t="s">
         <v>234</v>
       </c>
     </row>
@@ -8651,7 +8642,7 @@
         <v>10</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z13" s="130" t="s">
         <v>165</v>
@@ -8663,7 +8654,7 @@
         <v>10</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD13" s="130" t="s">
         <v>165</v>
@@ -8675,7 +8666,7 @@
         <v>10</v>
       </c>
       <c r="AG13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH13" s="130" t="s">
         <v>165</v>
@@ -8687,7 +8678,7 @@
         <v>10</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL13" s="130" t="s">
         <v>165</v>
@@ -8699,7 +8690,7 @@
         <v>10</v>
       </c>
       <c r="AO13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP13" s="130" t="s">
         <v>165</v>
@@ -8711,7 +8702,7 @@
         <v>10</v>
       </c>
       <c r="AS13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT13" s="12" t="s">
         <v>233</v>
@@ -8723,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="AW13" s="15" t="s">
-        <v>39</v>
+        <v>234</v>
       </c>
       <c r="AX13" s="131" t="s">
         <v>168</v>
@@ -8734,8 +8725,8 @@
       <c r="AZ13" s="133">
         <v>20</v>
       </c>
-      <c r="BA13" s="134" t="s">
-        <v>41</v>
+      <c r="BA13" s="119" t="s">
+        <v>40</v>
       </c>
       <c r="BB13" s="24" t="s">
         <v>233</v>
@@ -8750,26 +8741,26 @@
       <c r="BF13" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="BG13" s="135" t="s">
+      <c r="BG13" s="134" t="s">
         <v>233</v>
       </c>
       <c r="BH13" s="14">
         <v>15</v>
       </c>
-      <c r="BI13" s="136" t="s">
-        <v>41</v>
-      </c>
-      <c r="BJ13" s="163" t="s">
+      <c r="BI13" s="135" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ13" s="161" t="s">
         <v>164</v>
       </c>
-      <c r="BK13" s="164" t="s">
+      <c r="BK13" s="162" t="s">
         <v>233</v>
       </c>
-      <c r="BL13" s="165">
+      <c r="BL13" s="163">
         <v>15</v>
       </c>
-      <c r="BM13" s="166" t="s">
-        <v>41</v>
+      <c r="BM13" s="123" t="s">
+        <v>40</v>
       </c>
       <c r="BN13" s="12" t="s">
         <v>233</v>
@@ -8778,7 +8769,7 @@
         <v>233</v>
       </c>
       <c r="BP13" s="14"/>
-      <c r="BQ13" s="141" t="s">
+      <c r="BQ13" s="140" t="s">
         <v>234</v>
       </c>
       <c r="BR13" s="130" t="s">
@@ -8938,7 +8929,7 @@
         <v>10</v>
       </c>
       <c r="AW14" s="56" t="s">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="AX14" s="53" t="s">
         <v>169</v>
@@ -8972,9 +8963,9 @@
         <v>25</v>
       </c>
       <c r="BI14" s="99" t="s">
-        <v>41</v>
-      </c>
-      <c r="BJ14" s="144" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ14" s="143" t="s">
         <v>38</v>
       </c>
       <c r="BK14" s="54" t="s">
@@ -8983,8 +8974,8 @@
       <c r="BL14" s="55">
         <v>30</v>
       </c>
-      <c r="BM14" s="145" t="s">
-        <v>234</v>
+      <c r="BM14" s="144" t="s">
+        <v>40</v>
       </c>
       <c r="BN14" s="53" t="s">
         <v>233</v>
@@ -9003,7 +8994,7 @@
         <v>233</v>
       </c>
       <c r="BT14" s="55"/>
-      <c r="BU14" s="146" t="s">
+      <c r="BU14" s="145" t="s">
         <v>234</v>
       </c>
       <c r="BV14" s="57" t="s">
@@ -9013,7 +9004,7 @@
         <v>233</v>
       </c>
       <c r="BX14" s="55"/>
-      <c r="BY14" s="146" t="s">
+      <c r="BY14" s="145" t="s">
         <v>234</v>
       </c>
     </row>
@@ -16940,7 +16931,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="goaKi4LkTb2FiNc4klOFV4S8D0x7/y8tdbAVN9VoqyrdxvG0w/7J94e1HbtAlYXgAqD3z+NFYxVSFVowXKsGVw==" saltValue="iXzkBiPfzI2Un6XhsPWHlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="t9+PLNqOsAe6Xmoyz8I29jC/A24pVNAlFvju6F8a0giwU1SntF6kpzKZywsoX50Pp/MEBYCdmuY00ClD2ngCBQ==" saltValue="+KiuMSbpF/lNdZbZz43wsg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -16986,10 +16977,10 @@
       <c r="H3" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="227" t="s">
+      <c r="I3" s="226" t="s">
         <v>237</v>
       </c>
-      <c r="J3" s="228"/>
+      <c r="J3" s="227"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -17286,7 +17277,9 @@
       <c r="G20" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="228" t="s">
+        <v>305</v>
+      </c>
       <c r="I20" s="103" t="s">
         <v>257</v>
       </c>
@@ -17304,7 +17297,7 @@
       <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -17313,7 +17306,9 @@
       <c r="G21" t="s">
         <v>235</v>
       </c>
-      <c r="H21" s="1"/>
+      <c r="H21" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I21" s="103" t="s">
         <v>259</v>
       </c>
@@ -17331,13 +17326,15 @@
       <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
+      <c r="D22" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="I22" s="103" t="s">
         <v>67</v>
       </c>
@@ -17355,13 +17352,15 @@
       <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
+      <c r="D23" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I23" s="100" t="s">
         <v>70</v>
       </c>
@@ -17376,8 +17375,8 @@
       <c r="C24" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>232</v>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
@@ -17394,8 +17393,8 @@
       <c r="C25" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>59</v>
+      <c r="D25" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>235</v>
@@ -17408,9 +17407,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D26" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="I26" s="100" t="s">
         <v>63</v>
       </c>
@@ -17419,9 +17416,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D27" s="1" t="s">
-        <v>235</v>
-      </c>
+      <c r="D27" s="1"/>
       <c r="I27" s="103" t="s">
         <v>267</v>
       </c>
@@ -17452,7 +17447,7 @@
       <c r="C29" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="D29" s="137" t="s">
+      <c r="D29" s="136" t="s">
         <v>284</v>
       </c>
       <c r="E29" s="61" t="s">
@@ -17475,7 +17470,7 @@
       <c r="C30" t="s">
         <v>286</v>
       </c>
-      <c r="D30" s="138" t="s">
+      <c r="D30" s="137" t="s">
         <v>287</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -17498,7 +17493,7 @@
       <c r="C31" t="s">
         <v>288</v>
       </c>
-      <c r="D31" s="138" t="s">
+      <c r="D31" s="137" t="s">
         <v>289</v>
       </c>
       <c r="I31" s="100" t="s">
@@ -17518,7 +17513,7 @@
       <c r="C32" t="s">
         <v>290</v>
       </c>
-      <c r="D32" s="138" t="s">
+      <c r="D32" s="137" t="s">
         <v>291</v>
       </c>
       <c r="I32" s="100" t="s">
@@ -17715,7 +17710,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="94tb58x548tKRj1dr9747cwZuFd3avxhrSV986CJw9/6W5PAnYt8WfPpPBCRS23WmPH0ZEMS7Y6VSPF0BJWQ8Q==" saltValue="DdaPHgfOKbHnMbd2jvwA6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PlTu3BqFLGXzeMPxR99uO0GFTaWxV022zoY7RIqw3fxwP4FMyvAGLCYj6MFvEoMUbf0lSv1CcqNJkxDobG9CKA==" saltValue="qHplEhGQVoGL34yVDZqZ2g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -17724,36 +17719,41 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A21:A23">
-    <cfRule type="expression" priority="12">
+    <cfRule type="expression" priority="13">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:D9">
-    <cfRule type="expression" priority="13">
+    <cfRule type="expression" priority="14">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
-    <cfRule type="expression" priority="86">
+    <cfRule type="expression" priority="87">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I33">
+    <cfRule type="expression" priority="3">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
+    <cfRule type="expression" priority="4">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:J29">
+    <cfRule type="expression" priority="5">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J33">
     <cfRule type="expression" priority="2">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
-    <cfRule type="expression" priority="3">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I23:J29">
-    <cfRule type="expression" priority="4">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J33">
+  <conditionalFormatting sqref="H21:H22">
     <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
@@ -17764,6 +17764,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -17966,22 +17981,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17998,21 +18015,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/AutosurveillanceTemplates/PLUVIO.xlsx
+++ b/AutosurveillanceTemplates/PLUVIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9508395E-3F15-4379-AC02-DD433B5A979C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC6442E-BEFA-42AB-8412-91FC3F4324A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,8 +60,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="308">
   <si>
     <t>Pluviomètre</t>
   </si>
@@ -3334,7 +3356,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3816,6 +3838,9 @@
     <xf numFmtId="164" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3854,6 +3879,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4024,9 +4052,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4513,131 +4538,131 @@
     </row>
     <row r="2" spans="2:19" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="69"/>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="172" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
       <c r="S2" s="70"/>
     </row>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="69"/>
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="175" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="175"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="175" t="s">
+      <c r="D3" s="176"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="176" t="s">
         <v>201</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="175" t="s">
+      <c r="I3" s="176"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="176" t="s">
         <v>205</v>
       </c>
-      <c r="N3" s="175"/>
-      <c r="O3" s="175"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="176"/>
+      <c r="P3" s="170"/>
+      <c r="Q3" s="170"/>
+      <c r="R3" s="171"/>
       <c r="S3" s="70"/>
     </row>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="69"/>
-      <c r="C4" s="174" t="s">
+      <c r="C4" s="175" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="175" t="s">
+      <c r="D4" s="176"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="177"/>
+      <c r="H4" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="I4" s="175"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="176"/>
-      <c r="M4" s="175" t="s">
+      <c r="I4" s="176"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
+      <c r="L4" s="178"/>
+      <c r="M4" s="176" t="s">
         <v>194</v>
       </c>
-      <c r="N4" s="175"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="170"/>
+      <c r="N4" s="176"/>
+      <c r="O4" s="176"/>
+      <c r="P4" s="170"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="171"/>
       <c r="S4" s="70"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="69"/>
-      <c r="C5" s="174" t="s">
+      <c r="C5" s="175" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="175"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="175" t="s">
+      <c r="D5" s="176"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="175"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="175" t="s">
+      <c r="I5" s="176"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
+      <c r="L5" s="178"/>
+      <c r="M5" s="176" t="s">
         <v>206</v>
       </c>
-      <c r="N5" s="175"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="179"/>
-      <c r="Q5" s="179"/>
-      <c r="R5" s="180"/>
+      <c r="N5" s="176"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="181"/>
+      <c r="Q5" s="181"/>
+      <c r="R5" s="182"/>
       <c r="S5" s="70"/>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="69"/>
-      <c r="C6" s="181" t="s">
+      <c r="C6" s="183" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="182"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="182" t="s">
+      <c r="D6" s="184"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="184" t="s">
         <v>204</v>
       </c>
-      <c r="I6" s="182"/>
-      <c r="J6" s="183" t="str">
+      <c r="I6" s="184"/>
+      <c r="J6" s="185" t="str">
         <f>D25</f>
         <v>Pluviomètre</v>
       </c>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="182" t="s">
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="184" t="s">
         <v>207</v>
       </c>
-      <c r="N6" s="182"/>
-      <c r="O6" s="182"/>
-      <c r="P6" s="177"/>
-      <c r="Q6" s="177"/>
-      <c r="R6" s="178"/>
+      <c r="N6" s="184"/>
+      <c r="O6" s="184"/>
+      <c r="P6" s="179"/>
+      <c r="Q6" s="179"/>
+      <c r="R6" s="180"/>
       <c r="S6" s="70"/>
     </row>
     <row r="7" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -4662,24 +4687,24 @@
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="69"/>
-      <c r="C8" s="184" t="s">
+      <c r="C8" s="186" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="185"/>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
-      <c r="N8" s="185"/>
-      <c r="O8" s="185"/>
-      <c r="P8" s="185"/>
-      <c r="Q8" s="185"/>
-      <c r="R8" s="186"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
+      <c r="H8" s="187"/>
+      <c r="I8" s="187"/>
+      <c r="J8" s="187"/>
+      <c r="K8" s="187"/>
+      <c r="L8" s="187"/>
+      <c r="M8" s="187"/>
+      <c r="N8" s="187"/>
+      <c r="O8" s="187"/>
+      <c r="P8" s="187"/>
+      <c r="Q8" s="187"/>
+      <c r="R8" s="188"/>
       <c r="S8" s="70"/>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -4705,118 +4730,118 @@
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="69"/>
       <c r="C10" s="63"/>
-      <c r="D10" s="187" t="s">
+      <c r="D10" s="189" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="188"/>
-      <c r="F10" s="188"/>
-      <c r="G10" s="188"/>
-      <c r="H10" s="188"/>
-      <c r="I10" s="188"/>
-      <c r="J10" s="188"/>
-      <c r="K10" s="188"/>
-      <c r="L10" s="188"/>
-      <c r="M10" s="188"/>
-      <c r="N10" s="188"/>
-      <c r="O10" s="188"/>
-      <c r="P10" s="188"/>
-      <c r="Q10" s="189"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="190"/>
+      <c r="J10" s="190"/>
+      <c r="K10" s="190"/>
+      <c r="L10" s="190"/>
+      <c r="M10" s="190"/>
+      <c r="N10" s="190"/>
+      <c r="O10" s="190"/>
+      <c r="P10" s="190"/>
+      <c r="Q10" s="191"/>
       <c r="R10" s="64"/>
       <c r="S10" s="70"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="69"/>
       <c r="C11" s="77"/>
-      <c r="D11" s="190" t="s">
+      <c r="D11" s="192" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="191"/>
-      <c r="F11" s="192"/>
-      <c r="G11" s="166"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
-      <c r="J11" s="168"/>
-      <c r="K11" s="190" t="s">
+      <c r="E11" s="193"/>
+      <c r="F11" s="194"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="168"/>
+      <c r="I11" s="168"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="192" t="s">
         <v>211</v>
       </c>
-      <c r="L11" s="191"/>
-      <c r="M11" s="192"/>
-      <c r="N11" s="166"/>
-      <c r="O11" s="167"/>
-      <c r="P11" s="167"/>
-      <c r="Q11" s="168"/>
+      <c r="L11" s="193"/>
+      <c r="M11" s="194"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="168"/>
+      <c r="P11" s="168"/>
+      <c r="Q11" s="169"/>
       <c r="R11" s="78"/>
       <c r="S11" s="70"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="69"/>
       <c r="C12" s="77"/>
-      <c r="D12" s="190" t="s">
+      <c r="D12" s="192" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="191"/>
-      <c r="F12" s="192"/>
-      <c r="G12" s="166"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="168"/>
-      <c r="K12" s="190" t="s">
+      <c r="E12" s="193"/>
+      <c r="F12" s="194"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="168"/>
+      <c r="I12" s="168"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="192" t="s">
         <v>212</v>
       </c>
-      <c r="L12" s="191"/>
-      <c r="M12" s="192"/>
-      <c r="N12" s="166"/>
-      <c r="O12" s="167"/>
-      <c r="P12" s="167"/>
-      <c r="Q12" s="168"/>
+      <c r="L12" s="193"/>
+      <c r="M12" s="194"/>
+      <c r="N12" s="167"/>
+      <c r="O12" s="168"/>
+      <c r="P12" s="168"/>
+      <c r="Q12" s="169"/>
       <c r="R12" s="78"/>
       <c r="S12" s="70"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="69"/>
       <c r="C13" s="77"/>
-      <c r="D13" s="190" t="s">
+      <c r="D13" s="192" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="191"/>
-      <c r="F13" s="192"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="167"/>
-      <c r="I13" s="167"/>
-      <c r="J13" s="168"/>
-      <c r="K13" s="190" t="s">
+      <c r="E13" s="193"/>
+      <c r="F13" s="194"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="168"/>
+      <c r="I13" s="168"/>
+      <c r="J13" s="169"/>
+      <c r="K13" s="192" t="s">
         <v>213</v>
       </c>
-      <c r="L13" s="191"/>
-      <c r="M13" s="192"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="167"/>
-      <c r="P13" s="167"/>
-      <c r="Q13" s="168"/>
+      <c r="L13" s="193"/>
+      <c r="M13" s="194"/>
+      <c r="N13" s="167"/>
+      <c r="O13" s="168"/>
+      <c r="P13" s="168"/>
+      <c r="Q13" s="169"/>
       <c r="R13" s="78"/>
       <c r="S13" s="70"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="69"/>
       <c r="C14" s="77"/>
-      <c r="D14" s="190" t="s">
+      <c r="D14" s="192" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="191"/>
-      <c r="F14" s="192"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
-      <c r="I14" s="167"/>
-      <c r="J14" s="168"/>
-      <c r="K14" s="190" t="s">
+      <c r="E14" s="193"/>
+      <c r="F14" s="194"/>
+      <c r="G14" s="167"/>
+      <c r="H14" s="168"/>
+      <c r="I14" s="168"/>
+      <c r="J14" s="169"/>
+      <c r="K14" s="192" t="s">
         <v>214</v>
       </c>
-      <c r="L14" s="191"/>
-      <c r="M14" s="192"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="168"/>
+      <c r="L14" s="193"/>
+      <c r="M14" s="194"/>
+      <c r="N14" s="167"/>
+      <c r="O14" s="168"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="169"/>
       <c r="R14" s="78"/>
       <c r="S14" s="70"/>
     </row>
@@ -4830,15 +4855,15 @@
       <c r="H15" s="89"/>
       <c r="I15" s="89"/>
       <c r="J15" s="89"/>
-      <c r="K15" s="190" t="s">
+      <c r="K15" s="192" t="s">
         <v>231</v>
       </c>
-      <c r="L15" s="191"/>
-      <c r="M15" s="192"/>
-      <c r="N15" s="219"/>
-      <c r="O15" s="220"/>
-      <c r="P15" s="220"/>
-      <c r="Q15" s="221"/>
+      <c r="L15" s="193"/>
+      <c r="M15" s="194"/>
+      <c r="N15" s="221"/>
+      <c r="O15" s="222"/>
+      <c r="P15" s="222"/>
+      <c r="Q15" s="223"/>
       <c r="R15" s="78"/>
       <c r="S15" s="70"/>
     </row>
@@ -4865,14 +4890,14 @@
     <row r="17" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B17" s="69"/>
       <c r="C17" s="77"/>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="189" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="188"/>
-      <c r="F17" s="188"/>
-      <c r="G17" s="188"/>
-      <c r="H17" s="188"/>
-      <c r="I17" s="189"/>
+      <c r="E17" s="190"/>
+      <c r="F17" s="190"/>
+      <c r="G17" s="190"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="191"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -4887,18 +4912,18 @@
     <row r="18" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="69"/>
       <c r="C18" s="77"/>
-      <c r="D18" s="200" t="s">
+      <c r="D18" s="202" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="200"/>
-      <c r="F18" s="201" t="s">
+      <c r="E18" s="202"/>
+      <c r="F18" s="203" t="s">
         <v>178</v>
       </c>
-      <c r="G18" s="201"/>
-      <c r="H18" s="202" t="s">
+      <c r="G18" s="203"/>
+      <c r="H18" s="204" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="202"/>
+      <c r="I18" s="204"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -4913,15 +4938,15 @@
     <row r="19" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="69"/>
       <c r="C19" s="77"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="204" t="str">
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="205"/>
+      <c r="G19" s="205"/>
+      <c r="H19" s="206" t="str">
         <f>IF(D19&gt;0,D19-F19,"-")</f>
         <v>-</v>
       </c>
-      <c r="I19" s="204"/>
+      <c r="I19" s="206"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -4940,15 +4965,15 @@
     <row r="20" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="69"/>
       <c r="C20" s="77"/>
-      <c r="D20" s="197"/>
-      <c r="E20" s="197"/>
-      <c r="F20" s="197"/>
-      <c r="G20" s="197"/>
-      <c r="H20" s="198" t="str">
+      <c r="D20" s="199"/>
+      <c r="E20" s="199"/>
+      <c r="F20" s="199"/>
+      <c r="G20" s="199"/>
+      <c r="H20" s="200" t="str">
         <f>IF(D20&gt;0,D20-F20,"-")</f>
         <v>-</v>
       </c>
-      <c r="I20" s="198"/>
+      <c r="I20" s="200"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -5010,24 +5035,24 @@
     </row>
     <row r="23" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B23" s="69"/>
-      <c r="C23" s="184" t="s">
+      <c r="C23" s="186" t="s">
         <v>216</v>
       </c>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="185"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="185"/>
-      <c r="M23" s="185"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="185"/>
-      <c r="P23" s="185"/>
-      <c r="Q23" s="185"/>
-      <c r="R23" s="186"/>
+      <c r="D23" s="187"/>
+      <c r="E23" s="187"/>
+      <c r="F23" s="187"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="187"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="187"/>
+      <c r="L23" s="187"/>
+      <c r="M23" s="187"/>
+      <c r="N23" s="187"/>
+      <c r="O23" s="187"/>
+      <c r="P23" s="187"/>
+      <c r="Q23" s="187"/>
+      <c r="R23" s="188"/>
       <c r="S23" s="70"/>
     </row>
     <row r="24" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5053,46 +5078,46 @@
     <row r="25" spans="2:21" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B25" s="69"/>
       <c r="C25" s="63"/>
-      <c r="D25" s="199" t="s">
+      <c r="D25" s="201" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="199"/>
-      <c r="F25" s="199"/>
-      <c r="G25" s="199"/>
-      <c r="H25" s="199"/>
-      <c r="I25" s="199"/>
-      <c r="J25" s="199"/>
-      <c r="K25" s="199"/>
-      <c r="L25" s="199"/>
-      <c r="M25" s="199"/>
-      <c r="N25" s="199"/>
-      <c r="O25" s="199"/>
-      <c r="P25" s="199"/>
-      <c r="Q25" s="199"/>
+      <c r="E25" s="201"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="201"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="201"/>
+      <c r="K25" s="201"/>
+      <c r="L25" s="201"/>
+      <c r="M25" s="201"/>
+      <c r="N25" s="201"/>
+      <c r="O25" s="201"/>
+      <c r="P25" s="201"/>
+      <c r="Q25" s="201"/>
       <c r="R25" s="64"/>
       <c r="S25" s="70"/>
     </row>
     <row r="26" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="69"/>
       <c r="C26" s="63"/>
-      <c r="D26" s="193" t="s">
+      <c r="D26" s="195" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="194"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="194"/>
-      <c r="I26" s="195"/>
-      <c r="J26" s="193" t="s">
+      <c r="E26" s="196"/>
+      <c r="F26" s="196"/>
+      <c r="G26" s="196"/>
+      <c r="H26" s="196"/>
+      <c r="I26" s="197"/>
+      <c r="J26" s="195" t="s">
         <v>174</v>
       </c>
-      <c r="K26" s="194"/>
-      <c r="L26" s="194"/>
-      <c r="M26" s="195"/>
-      <c r="N26" s="196" t="s">
+      <c r="K26" s="196"/>
+      <c r="L26" s="196"/>
+      <c r="M26" s="197"/>
+      <c r="N26" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="O26" s="196"/>
+      <c r="O26" s="198"/>
       <c r="P26" s="82" t="s">
         <v>189</v>
       </c>
@@ -5111,23 +5136,23 @@
       <c r="D27" s="83">
         <v>1</v>
       </c>
-      <c r="E27" s="213" t="str">
+      <c r="E27" s="215" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D27+2,FALSE),"")</f>
         <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
       </c>
-      <c r="F27" s="214"/>
-      <c r="G27" s="214"/>
-      <c r="H27" s="214"/>
-      <c r="I27" s="214"/>
-      <c r="J27" s="213" t="str">
+      <c r="F27" s="216"/>
+      <c r="G27" s="216"/>
+      <c r="H27" s="216"/>
+      <c r="I27" s="216"/>
+      <c r="J27" s="215" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D27+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
       </c>
-      <c r="K27" s="214"/>
-      <c r="L27" s="214"/>
-      <c r="M27" s="215"/>
-      <c r="N27" s="216"/>
-      <c r="O27" s="217"/>
+      <c r="K27" s="216"/>
+      <c r="L27" s="216"/>
+      <c r="M27" s="217"/>
+      <c r="N27" s="218"/>
+      <c r="O27" s="219"/>
       <c r="P27" s="84">
         <f>IF(OR(N27="Validé",N27="Réserve",N27="Oui"),Q27,0)</f>
         <v>0</v>
@@ -5138,8 +5163,9 @@
       </c>
       <c r="R27" s="64"/>
       <c r="S27" s="70"/>
-      <c r="U27" s="165" t="s">
-        <v>40</v>
+      <c r="U27" s="165" t="str" cm="1">
+        <f t="array" ref="U27">IFERROR(INDEX(Critères!$B$3:$BZ$16, D27+2, MATCH($D$25, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="28" spans="2:21" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5148,26 +5174,26 @@
       <c r="D28" s="83">
         <v>2</v>
       </c>
-      <c r="E28" s="213" t="str">
+      <c r="E28" s="215" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D28+2,FALSE),"")</f>
         <v>Le pluviomètre présente t-il une section suffisante ?</v>
       </c>
-      <c r="F28" s="214"/>
-      <c r="G28" s="214"/>
-      <c r="H28" s="214"/>
-      <c r="I28" s="214"/>
-      <c r="J28" s="213" t="str">
+      <c r="F28" s="216"/>
+      <c r="G28" s="216"/>
+      <c r="H28" s="216"/>
+      <c r="I28" s="216"/>
+      <c r="J28" s="215" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D28+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Entre 180 et 1 000 cm2, soit un diamètre variant entre 15 et 35 cm.</v>
       </c>
-      <c r="K28" s="214"/>
-      <c r="L28" s="214"/>
-      <c r="M28" s="215"/>
-      <c r="N28" s="216" t="str">
+      <c r="K28" s="216"/>
+      <c r="L28" s="216"/>
+      <c r="M28" s="217"/>
+      <c r="N28" s="218" t="str">
         <f>IF(N13&lt;&gt;"",IF(AND(N13&gt;=15,N13&lt;=35),"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O28" s="217"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="84">
         <f t="shared" ref="P28:P31" si="0">IF(OR(N28="Validé",N28="Réserve",N28="Oui"),Q28,0)</f>
         <v>0</v>
@@ -5178,8 +5204,9 @@
       </c>
       <c r="R28" s="64"/>
       <c r="S28" s="70"/>
-      <c r="U28" s="165" t="s">
-        <v>40</v>
+      <c r="U28" s="165" t="str" cm="1">
+        <f t="array" ref="U28">IFERROR(INDEX(Critères!$B$3:$BZ$16, D28+2, MATCH($D$25, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="29" spans="2:21" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5188,23 +5215,23 @@
       <c r="D29" s="83">
         <v>3</v>
       </c>
-      <c r="E29" s="213" t="str">
+      <c r="E29" s="215" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D29+2,FALSE),"")</f>
         <v>Le pluviomètre est-il installé conformément aux règles de l'art et/ou aux prescriptions des constructeurs ?</v>
       </c>
-      <c r="F29" s="214"/>
-      <c r="G29" s="214"/>
-      <c r="H29" s="214"/>
-      <c r="I29" s="214"/>
-      <c r="J29" s="213" t="str">
+      <c r="F29" s="216"/>
+      <c r="G29" s="216"/>
+      <c r="H29" s="216"/>
+      <c r="I29" s="216"/>
+      <c r="J29" s="215" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D29+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Sur une surface horizontale, entre 0,5 et 2 mètres du sol (1 mètre recommandé), à une distance supérieure à 4 fois la hauteur d'obstacles (mur, arbres, etc…).</v>
       </c>
-      <c r="K29" s="214"/>
-      <c r="L29" s="214"/>
-      <c r="M29" s="215"/>
-      <c r="N29" s="216"/>
-      <c r="O29" s="217"/>
+      <c r="K29" s="216"/>
+      <c r="L29" s="216"/>
+      <c r="M29" s="217"/>
+      <c r="N29" s="218"/>
+      <c r="O29" s="219"/>
       <c r="P29" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5215,8 +5242,9 @@
       </c>
       <c r="R29" s="64"/>
       <c r="S29" s="70"/>
-      <c r="U29" s="165" t="s">
-        <v>40</v>
+      <c r="U29" s="165" t="str" cm="1">
+        <f t="array" ref="U29">IFERROR(INDEX(Critères!$B$3:$BZ$16, D29+2, MATCH($D$25, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="30" spans="2:21" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5225,24 +5253,24 @@
       <c r="D30" s="83">
         <v>4</v>
       </c>
-      <c r="E30" s="213" t="str">
+      <c r="E30" s="215" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D30+2,FALSE),"")</f>
         <v>La propreté et l'état d'entretien du pluviomètre, sont-ils satisfaisants ?</v>
       </c>
-      <c r="F30" s="214"/>
-      <c r="G30" s="214"/>
-      <c r="H30" s="214"/>
-      <c r="I30" s="214"/>
-      <c r="J30" s="213" t="str">
+      <c r="F30" s="216"/>
+      <c r="G30" s="216"/>
+      <c r="H30" s="216"/>
+      <c r="I30" s="216"/>
+      <c r="J30" s="215" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D30+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
 Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
       </c>
-      <c r="K30" s="214"/>
-      <c r="L30" s="214"/>
-      <c r="M30" s="215"/>
-      <c r="N30" s="216"/>
-      <c r="O30" s="217"/>
+      <c r="K30" s="216"/>
+      <c r="L30" s="216"/>
+      <c r="M30" s="217"/>
+      <c r="N30" s="218"/>
+      <c r="O30" s="219"/>
       <c r="P30" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5253,8 +5281,9 @@
       </c>
       <c r="R30" s="64"/>
       <c r="S30" s="70"/>
-      <c r="U30" s="165" t="s">
-        <v>40</v>
+      <c r="U30" s="165" t="str" cm="1">
+        <f t="array" ref="U30">IFERROR(INDEX(Critères!$B$3:$BZ$16, D30+2, MATCH($D$25, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="31" spans="2:21" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5263,26 +5292,26 @@
       <c r="D31" s="83">
         <v>5</v>
       </c>
-      <c r="E31" s="213" t="str">
+      <c r="E31" s="215" t="str">
         <f>IFERROR(HLOOKUP($D$25,Critères!$B$3:$BY$16,D31+2,FALSE),"")</f>
         <v>L'écart entre d'une part la mesure de la hauteur de pluie réalisée à partir du dispositif en place et celle réalisée par l'organisme de contrôle d'autre part, est-il cohérent (EMT ± 1 unité) ?</v>
       </c>
-      <c r="F31" s="214"/>
-      <c r="G31" s="214"/>
-      <c r="H31" s="214"/>
-      <c r="I31" s="214"/>
-      <c r="J31" s="213" t="str">
+      <c r="F31" s="216"/>
+      <c r="G31" s="216"/>
+      <c r="H31" s="216"/>
+      <c r="I31" s="216"/>
+      <c r="J31" s="215" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D31+2, MATCH($D$25, Critères!$B$3:$BY$3, 0) + 1),"")</f>
         <v>-</v>
       </c>
-      <c r="K31" s="214"/>
-      <c r="L31" s="214"/>
-      <c r="M31" s="215"/>
-      <c r="N31" s="216" t="str">
+      <c r="K31" s="216"/>
+      <c r="L31" s="216"/>
+      <c r="M31" s="217"/>
+      <c r="N31" s="218" t="str">
         <f>U21</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O31" s="217"/>
+      <c r="O31" s="219"/>
       <c r="P31" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5293,57 +5322,58 @@
       </c>
       <c r="R31" s="64"/>
       <c r="S31" s="70"/>
-      <c r="U31" s="165" t="s">
-        <v>40</v>
+      <c r="U31" s="165" t="str" cm="1">
+        <f t="array" ref="U31">IFERROR(INDEX(Critères!$B$3:$BZ$16, D31+2, MATCH($D$25, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="69"/>
       <c r="C32" s="63"/>
-      <c r="D32" s="218" t="s">
+      <c r="D32" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="218"/>
-      <c r="F32" s="218"/>
-      <c r="G32" s="218"/>
-      <c r="H32" s="218"/>
-      <c r="I32" s="218"/>
-      <c r="J32" s="218"/>
-      <c r="K32" s="218"/>
-      <c r="L32" s="218"/>
-      <c r="M32" s="218"/>
-      <c r="N32" s="212"/>
-      <c r="O32" s="212"/>
-      <c r="P32" s="212" t="s">
+      <c r="E32" s="220"/>
+      <c r="F32" s="220"/>
+      <c r="G32" s="220"/>
+      <c r="H32" s="220"/>
+      <c r="I32" s="220"/>
+      <c r="J32" s="220"/>
+      <c r="K32" s="220"/>
+      <c r="L32" s="220"/>
+      <c r="M32" s="220"/>
+      <c r="N32" s="214"/>
+      <c r="O32" s="214"/>
+      <c r="P32" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="Q32" s="212"/>
+      <c r="Q32" s="214"/>
       <c r="R32" s="64"/>
       <c r="S32" s="70"/>
     </row>
     <row r="33" spans="2:19" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="69"/>
       <c r="C33" s="63"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="222"/>
-      <c r="K33" s="222"/>
-      <c r="L33" s="222"/>
-      <c r="M33" s="222"/>
-      <c r="N33" s="223" t="str">
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="224"/>
+      <c r="J33" s="224"/>
+      <c r="K33" s="224"/>
+      <c r="L33" s="224"/>
+      <c r="M33" s="224"/>
+      <c r="N33" s="225" t="str">
         <f>IF(P33&gt;80,"Validé",IF(P33&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O33" s="223"/>
-      <c r="P33" s="224">
+      <c r="O33" s="225"/>
+      <c r="P33" s="226">
         <f>IF(SUM(P27:P31)&gt;100,100,SUM(P27:P31))</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="225"/>
+      <c r="Q33" s="227"/>
       <c r="R33" s="64"/>
       <c r="S33" s="70"/>
     </row>
@@ -5389,124 +5419,124 @@
     </row>
     <row r="36" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="69"/>
-      <c r="C36" s="184" t="s">
+      <c r="C36" s="186" t="s">
         <v>217</v>
       </c>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="185"/>
-      <c r="J36" s="185"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="185"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="185"/>
-      <c r="O36" s="185"/>
-      <c r="P36" s="185"/>
-      <c r="Q36" s="185"/>
-      <c r="R36" s="186"/>
+      <c r="D36" s="187"/>
+      <c r="E36" s="187"/>
+      <c r="F36" s="187"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="187"/>
+      <c r="K36" s="187"/>
+      <c r="L36" s="187"/>
+      <c r="M36" s="187"/>
+      <c r="N36" s="187"/>
+      <c r="O36" s="187"/>
+      <c r="P36" s="187"/>
+      <c r="Q36" s="187"/>
+      <c r="R36" s="188"/>
       <c r="S36" s="70"/>
     </row>
     <row r="37" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B37" s="69"/>
-      <c r="C37" s="205"/>
-      <c r="D37" s="206"/>
-      <c r="E37" s="206"/>
-      <c r="F37" s="206"/>
-      <c r="G37" s="206"/>
-      <c r="H37" s="206"/>
-      <c r="I37" s="206"/>
-      <c r="J37" s="206"/>
-      <c r="K37" s="206"/>
-      <c r="L37" s="206"/>
-      <c r="M37" s="206"/>
-      <c r="N37" s="206"/>
-      <c r="O37" s="206"/>
-      <c r="P37" s="206"/>
-      <c r="Q37" s="206"/>
-      <c r="R37" s="207"/>
+      <c r="C37" s="207"/>
+      <c r="D37" s="208"/>
+      <c r="E37" s="208"/>
+      <c r="F37" s="208"/>
+      <c r="G37" s="208"/>
+      <c r="H37" s="208"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="208"/>
+      <c r="N37" s="208"/>
+      <c r="O37" s="208"/>
+      <c r="P37" s="208"/>
+      <c r="Q37" s="208"/>
+      <c r="R37" s="209"/>
       <c r="S37" s="70"/>
     </row>
     <row r="38" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="69"/>
-      <c r="C38" s="208"/>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="206"/>
-      <c r="I38" s="206"/>
-      <c r="J38" s="206"/>
-      <c r="K38" s="206"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="206"/>
-      <c r="O38" s="206"/>
-      <c r="P38" s="206"/>
-      <c r="Q38" s="206"/>
-      <c r="R38" s="207"/>
+      <c r="C38" s="210"/>
+      <c r="D38" s="208"/>
+      <c r="E38" s="208"/>
+      <c r="F38" s="208"/>
+      <c r="G38" s="208"/>
+      <c r="H38" s="208"/>
+      <c r="I38" s="208"/>
+      <c r="J38" s="208"/>
+      <c r="K38" s="208"/>
+      <c r="L38" s="208"/>
+      <c r="M38" s="208"/>
+      <c r="N38" s="208"/>
+      <c r="O38" s="208"/>
+      <c r="P38" s="208"/>
+      <c r="Q38" s="208"/>
+      <c r="R38" s="209"/>
       <c r="S38" s="70"/>
     </row>
     <row r="39" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="69"/>
-      <c r="C39" s="208"/>
-      <c r="D39" s="206"/>
-      <c r="E39" s="206"/>
-      <c r="F39" s="206"/>
-      <c r="G39" s="206"/>
-      <c r="H39" s="206"/>
-      <c r="I39" s="206"/>
-      <c r="J39" s="206"/>
-      <c r="K39" s="206"/>
-      <c r="L39" s="206"/>
-      <c r="M39" s="206"/>
-      <c r="N39" s="206"/>
-      <c r="O39" s="206"/>
-      <c r="P39" s="206"/>
-      <c r="Q39" s="206"/>
-      <c r="R39" s="207"/>
+      <c r="C39" s="210"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="208"/>
+      <c r="H39" s="208"/>
+      <c r="I39" s="208"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="208"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="208"/>
+      <c r="N39" s="208"/>
+      <c r="O39" s="208"/>
+      <c r="P39" s="208"/>
+      <c r="Q39" s="208"/>
+      <c r="R39" s="209"/>
       <c r="S39" s="70"/>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="69"/>
-      <c r="C40" s="208"/>
-      <c r="D40" s="206"/>
-      <c r="E40" s="206"/>
-      <c r="F40" s="206"/>
-      <c r="G40" s="206"/>
-      <c r="H40" s="206"/>
-      <c r="I40" s="206"/>
-      <c r="J40" s="206"/>
-      <c r="K40" s="206"/>
-      <c r="L40" s="206"/>
-      <c r="M40" s="206"/>
-      <c r="N40" s="206"/>
-      <c r="O40" s="206"/>
-      <c r="P40" s="206"/>
-      <c r="Q40" s="206"/>
-      <c r="R40" s="207"/>
+      <c r="C40" s="210"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="209"/>
       <c r="S40" s="70"/>
     </row>
     <row r="41" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B41" s="69"/>
-      <c r="C41" s="209"/>
-      <c r="D41" s="210"/>
-      <c r="E41" s="210"/>
-      <c r="F41" s="210"/>
-      <c r="G41" s="210"/>
-      <c r="H41" s="210"/>
-      <c r="I41" s="210"/>
-      <c r="J41" s="210"/>
-      <c r="K41" s="210"/>
-      <c r="L41" s="210"/>
-      <c r="M41" s="210"/>
-      <c r="N41" s="210"/>
-      <c r="O41" s="210"/>
-      <c r="P41" s="210"/>
-      <c r="Q41" s="210"/>
-      <c r="R41" s="211"/>
+      <c r="C41" s="211"/>
+      <c r="D41" s="212"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="212"/>
+      <c r="G41" s="212"/>
+      <c r="H41" s="212"/>
+      <c r="I41" s="212"/>
+      <c r="J41" s="212"/>
+      <c r="K41" s="212"/>
+      <c r="L41" s="212"/>
+      <c r="M41" s="212"/>
+      <c r="N41" s="212"/>
+      <c r="O41" s="212"/>
+      <c r="P41" s="212"/>
+      <c r="Q41" s="212"/>
+      <c r="R41" s="213"/>
       <c r="S41" s="70"/>
     </row>
     <row r="42" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5530,7 +5560,7 @@
       <c r="S42" s="73"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Wc9AwwZGrSXNoq0x7LZfwq727AgMT+WcTTreH3X1mWNJkimZ2wMXkI5ISY3Xdn1/hG76ggf9nbYSQbyVVRDgIw==" saltValue="1nzoJxCNJFTEFDhb9WkWfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BGPcS5xV8jnyvZw4mtIeAwzErcI73SzX+EniNaYnnB+GUrPA9yvzANVb55JmaBYfhv7ku05oUEHPCAxqnvwOdA==" saltValue="nHHIMjfabRCsUPJxxQhPuQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="83">
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="N15:Q15"/>
@@ -16931,7 +16961,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="t9+PLNqOsAe6Xmoyz8I29jC/A24pVNAlFvju6F8a0giwU1SntF6kpzKZywsoX50Pp/MEBYCdmuY00ClD2ngCBQ==" saltValue="+KiuMSbpF/lNdZbZz43wsg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7vBhGqEgjPWJMLsWDIfYNiGqgiVy8+6eBGGQb+57JAmcf0fVS2GzfWaPxJTk0oc+/HKMPwIUgy1/g4zOhMf/mg==" saltValue="1eKxhOh7dqjpNjDdbTQcfA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -16977,10 +17007,10 @@
       <c r="H3" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="226" t="s">
+      <c r="I3" s="228" t="s">
         <v>237</v>
       </c>
-      <c r="J3" s="227"/>
+      <c r="J3" s="229"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -17277,7 +17307,7 @@
       <c r="G20" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="H20" s="228" t="s">
+      <c r="H20" s="166" t="s">
         <v>305</v>
       </c>
       <c r="I20" s="103" t="s">
@@ -17710,7 +17740,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PlTu3BqFLGXzeMPxR99uO0GFTaWxV022zoY7RIqw3fxwP4FMyvAGLCYj6MFvEoMUbf0lSv1CcqNJkxDobG9CKA==" saltValue="qHplEhGQVoGL34yVDZqZ2g==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="msLUVGm8jO8TMv0cNEuWYs0s15AFUMIMnpnYvZ73fhXQAnHJqgaS+uI4RCvwpFIGeM1QqqJbCv/6WlU3EIaDeg==" saltValue="NMnUCriqWrlpQcw1bFjVvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -17730,6 +17760,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
     <cfRule type="expression" priority="87">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H22">
+    <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17753,32 +17788,12 @@
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="expression" priority="1">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -17981,24 +17996,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18015,4 +18028,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>